--- a/exemples/preferencies-30-alumnes-complet.xlsx
+++ b/exemples/preferencies-30-alumnes-complet.xlsx
@@ -36,8 +36,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="9" width="30" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -68,20 +68,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Competència (1-10)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Amb qui vols treballar? (1a opció)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Amb qui vols treballar? (2a opció)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Amb qui vols treballar? (3a opció)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Amb qui prefereixes NO coincidir? (Separar 1)</t>
         </is>
@@ -110,15 +115,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7,5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Berta Camps Roig</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ona Freixes Marí</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ivet Molins Ferrer</t>
         </is>
@@ -147,15 +157,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Biel Sala Monfort</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lluc Amat Pujol</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">Nil Casals Duran</t>
         </is>
@@ -184,20 +199,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Aina Bosch Prat</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ona Freixes Marí</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">Carla Ruiz Bonet</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">Marçal Gibert Soler</t>
         </is>
@@ -231,15 +251,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t xml:space="preserve">3,5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Arnau Ferrer Vidal</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Nil Casals Duran</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">Lluc Amat Pujol</t>
         </is>
@@ -268,15 +293,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Berta Camps Roig</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ivet Molins Ferrer</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">Aina Bosch Prat</t>
         </is>
@@ -305,15 +335,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Enric Vila Camps</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">Guim Peris Nadal</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">Arnau Ferrer Vidal</t>
         </is>
@@ -342,15 +377,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t xml:space="preserve">5,5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ivet Molins Ferrer</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">Júlia Bofill Tena</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">Carla Ruiz Bonet</t>
         </is>
@@ -379,15 +419,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t xml:space="preserve">2,5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dani Oliva Serra</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Guim Peris Nadal</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">Pol Maset Rius</t>
         </is>
@@ -421,15 +466,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t xml:space="preserve">4,5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nil Casals Duran</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">Biel Sala Monfort</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">Roc Fabra Tur</t>
         </is>
@@ -458,15 +508,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Helena Duran Mas</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">Júlia Bofill Tena</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">Laia Morera Font</t>
         </is>
@@ -495,20 +550,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t xml:space="preserve">8,5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dani Oliva Serra</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">Enric Vila Camps</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">Pol Maset Rius</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ferran Aymar Lluch</t>
         </is>
@@ -537,15 +597,20 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t xml:space="preserve">6,5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gemma Sendra Prats</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">Laia Morera Font</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">Marta Espí Vidal</t>
         </is>
@@ -574,15 +639,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elna Piera Costa</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">Aina Bosch Prat</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">Carla Ruiz Bonet</t>
         </is>
@@ -611,15 +681,20 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lluc Amat Pujol</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">Roc Fabra Tur</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">Arnau Ferrer Vidal</t>
         </is>
@@ -653,15 +728,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t xml:space="preserve">9,5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gemma Sendra Prats</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">Elna Piera Costa</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">Helena Duran Mas</t>
         </is>
@@ -690,15 +770,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jordi Benet Puig</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">Arnau Ferrer Vidal</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">Biel Sala Monfort</t>
         </is>
@@ -727,15 +812,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t xml:space="preserve">7,5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Helena Duran Mas</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">Gemma Sendra Prats</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nora Vendrell Aran</t>
         </is>
@@ -764,20 +854,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Pol Maset Rius</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">Quim Batlle Sanç</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">Dani Oliva Serra</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">Berta Camps Roig</t>
         </is>
@@ -806,15 +901,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nora Vendrell Aran</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ona Freixes Marí</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">Helena Duran Mas</t>
         </is>
@@ -843,15 +943,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ferran Aymar Lluch</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">Biel Sala Monfort</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">Jordi Benet Puig</t>
         </is>
@@ -880,15 +985,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Marta Espí Vidal</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">Laia Morera Font</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ona Freixes Marí</t>
         </is>
@@ -922,15 +1032,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t xml:space="preserve">3,5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Aina Bosch Prat</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">Berta Camps Roig</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nora Vendrell Aran</t>
         </is>
@@ -959,15 +1074,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Marçal Gibert Soler</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">Enric Vila Camps</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">Quim Batlle Sanç</t>
         </is>
@@ -996,15 +1116,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t xml:space="preserve">6,5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Pol Maset Rius</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">Marçal Gibert Soler</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">Guim Peris Nadal</t>
         </is>
@@ -1033,15 +1158,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t xml:space="preserve">4,5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jordi Benet Puig</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ferran Aymar Lluch</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nil Casals Duran</t>
         </is>
@@ -1070,15 +1200,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sara Miret Badia</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">Laia Morera Font</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">Txell Roig Cases</t>
         </is>
@@ -1112,15 +1247,20 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t xml:space="preserve">8,5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rita Nogués Clua</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">Txell Roig Cases</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gemma Sendra Prats</t>
         </is>
@@ -1149,15 +1289,20 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t xml:space="preserve">5,5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rita Nogués Clua</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara Miret Badia</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">Marta Espí Vidal</t>
         </is>
@@ -1186,15 +1331,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Quim Batlle Sanç</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">Vidal Cortès Pi</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">Pol Maset Rius</t>
         </is>
@@ -1223,15 +1373,20 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Unai Ferré Roca</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">Roc Fabra Tur</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">Lluc Amat Pujol</t>
         </is>
